--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.46.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: the subp Ã¦ na to hear judgment, is not now in f</t>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: iff â€˜s bill is,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L28: isolated marker/symbol line :: U</t>
@@ -618,13 +622,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]39 *</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: -- â€”69th Order says that Â« The party setting down a 69th new Order</t>
+          <t>L53: punctuation artifact: double/multiple hyphen :: -- —69th Order says that « The party setting down a 69th new Order</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,16 +662,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ cenas to hear judgment. The rule does</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: -- â€”69th Order says that Â« The party setting down a 69th new Order</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -675,7 +671,11 @@
           <t>L34: isolated marker/symbol line :: 39</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L91: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -709,19 +709,15 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: notice or Subp Ã¦ na in respect of demurrers, and</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: practice :â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
+        </is>
+      </c>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
@@ -742,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -756,11 +752,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 69th Order says that â€œThe party setting</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -799,11 +791,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Cause " &amp; c., must sue out a Subp Ã¦ na, but i</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -842,11 +830,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na, but it does not</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -885,11 +869,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subp Ã¦ na ad</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -953,12 +933,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -997,7 +977,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1031,12 +1011,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
